--- a/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:05</t>
+    <t xml:space="preserve">2026-09-09 22:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:01</t>
+    <t xml:space="preserve">2026-09-17 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1606571.88</v>
+        <v>1457645.12</v>
       </c>
     </row>
     <row r="3">
@@ -1115,26 +1115,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1158183.88</v>
+        <v>1606571.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1076358.62</v>
+        <v>1158183.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1457645.12</v>
+        <v>1076358.62</v>
       </c>
     </row>
     <row r="7">
@@ -1175,35 +1175,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1334637.75</v>
+        <v>1217673.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1487986.88</v>
+        <v>1359459.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1606571.88</v>
+        <v>1457645.12</v>
       </c>
     </row>
     <row r="5">
@@ -1241,101 +1241,101 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>968522</v>
+        <v>1334637.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1085860</v>
+        <v>1487986.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1158183.88</v>
+        <v>1606571.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>888122</v>
+        <v>968522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1006140.5</v>
+        <v>1085860</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1076358.62</v>
+        <v>1158183.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1217673.75</v>
+        <v>888122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1359459.5</v>
+        <v>1006140.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1457645.12</v>
+        <v>1076358.62</v>
       </c>
     </row>
     <row r="17">

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:34</t>
+    <t xml:space="preserve">2026-09-25 21:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -602,7 +602,7 @@
         <v>998037.31</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>64009.07</v>
+        <v>64009.06</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>6.41</v>
@@ -694,7 +694,7 @@
         <v>1212712.25</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>70411.63</v>
+        <v>70411.62</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>5.81</v>
@@ -740,7 +740,7 @@
         <v>1051526.25</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>63584.13</v>
+        <v>63584.12</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>6.05</v>
@@ -763,7 +763,7 @@
         <v>1220706.12</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>82894.26</v>
+        <v>82894.25</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>6.79</v>
@@ -786,7 +786,7 @@
         <v>1150350.12</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>75137.76</v>
+        <v>75137.75</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>6.53</v>
@@ -855,7 +855,7 @@
         <v>1311674.25</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>92771.87</v>
+        <v>92771.88</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>7.07</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_metropolitana.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:34</t>
+    <t xml:space="preserve">2026-10-05 07:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -597,7 +597,7 @@
         <v>1076359</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1006140</v>
+        <v>1006141</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>-23.4</v>
@@ -742,7 +742,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1347718</v>
+        <v>1347719</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1550812</v>
@@ -787,7 +787,7 @@
         <v>1062046</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1229306</v>
+        <v>1229307</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>-13.6</v>
